--- a/Results/results.xlsx
+++ b/Results/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,12 +508,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
+          <t>A Life Tribute Funeral Care - Largo</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>caacn</t>
+          <t>flall</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -533,12 +533,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
+          <t>A Life Tribute Funeral Care - Largo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>caacn</t>
+          <t>flall</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -558,12 +558,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
+          <t>A Life Tribute Funeral Care - Largo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>caacn</t>
+          <t>flall</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -583,12 +583,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
+          <t>A Life Tribute Funeral Care - Largo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>caacn</t>
+          <t>flall</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,12 +608,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
+          <t>A Life Tribute Funeral Care - Largo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>caacn</t>
+          <t>flall</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -633,12 +633,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
+          <t>A Life Tribute Funeral Care - Largo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>caacn</t>
+          <t>flall</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -658,12 +658,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
+          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>caacs</t>
+          <t>caacn</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -683,12 +683,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
+          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>caacs</t>
+          <t>caacn</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -708,12 +708,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
+          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>caacs</t>
+          <t>caacn</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -733,12 +733,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
+          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>caacs</t>
+          <t>caacn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -758,12 +758,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
+          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>caacs</t>
+          <t>caacn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -783,12 +783,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
+          <t>Affordable Cremation &amp; Funeral Center - North Sacramento</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>caacs</t>
+          <t>caacn</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -808,17 +808,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Service - Roseville</t>
+          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>caacr</t>
+          <t>caacs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -833,17 +833,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Service - Roseville</t>
+          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>caacr</t>
+          <t>caacs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -852,23 +852,23 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Affordable Cremation &amp; Funeral Service - Roseville</t>
+          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>caacr</t>
+          <t>caacs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -877,23 +877,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Affordable Mortuary</t>
+          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cabam</t>
+          <t>caacs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -902,23 +902,23 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Affordable Mortuary</t>
+          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cabam</t>
+          <t>caacs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -933,17 +933,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Affordable Mortuary</t>
+          <t>Affordable Cremation &amp; Funeral Center - South Sacramento</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cabam</t>
+          <t>caacs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -952,18 +952,18 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Affordable Mortuary</t>
+          <t>Affordable Cremation &amp; Funeral Service - Roseville</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cabam</t>
+          <t>caacr</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -977,18 +977,18 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Affordable Mortuary</t>
+          <t>Affordable Cremation &amp; Funeral Service - Roseville</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cabam</t>
+          <t>caacr</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1002,18 +1002,18 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Affordable Mortuary</t>
+          <t>Affordable Cremation &amp; Funeral Service - Roseville</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cabam</t>
+          <t>caacr</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1033,12 +1033,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
+          <t>Affordable Mortuary</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>coavl</t>
+          <t>cabam</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1052,18 +1052,18 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
+          <t>Affordable Mortuary</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>coavl</t>
+          <t>cabam</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1077,18 +1077,18 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
+          <t>Affordable Mortuary</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>coavl</t>
+          <t>cabam</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1108,12 +1108,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
+          <t>Affordable Mortuary</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>coavl</t>
+          <t>cabam</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1127,18 +1127,18 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
+          <t>Affordable Mortuary</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>coavl</t>
+          <t>cabam</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1158,12 +1158,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
+          <t>Affordable Mortuary</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>coavl</t>
+          <t>cabam</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1177,18 +1177,18 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>coavc</t>
+          <t>coavl</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1208,12 +1208,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>coavc</t>
+          <t>coavl</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1233,12 +1233,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>coavc</t>
+          <t>coavl</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1258,12 +1258,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>coavc</t>
+          <t>coavl</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1277,18 +1277,18 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>coavc</t>
+          <t>coavl</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1308,12 +1308,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Centennial</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>coavc</t>
+          <t>coavl</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1327,18 +1327,18 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
+          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>coavw</t>
+          <t>coavc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1358,12 +1358,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
+          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>coavw</t>
+          <t>coavc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1383,12 +1383,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
+          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>coavw</t>
+          <t>coavc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1408,12 +1408,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
+          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>coavw</t>
+          <t>coavc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1427,18 +1427,18 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
+          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>coavw</t>
+          <t>coavc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1458,12 +1458,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
+          <t>All Veterans Funeral &amp; Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>coavw</t>
+          <t>coavc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1477,18 +1477,18 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
+          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>coavr</t>
+          <t>coavw</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
+          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>coavr</t>
+          <t>coavw</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1533,12 +1533,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
+          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>coavr</t>
+          <t>coavw</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1558,12 +1558,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
+          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>coavr</t>
+          <t>coavw</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
+          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>coavr</t>
+          <t>coavw</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1608,12 +1608,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
+          <t>All Veterans Funeral &amp; Cremation - Westminster</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>coavr</t>
+          <t>coavw</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>All-States Cremation - Centennial</t>
+          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>coasl</t>
+          <t>coavr</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1652,23 +1652,23 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>All-States Cremation - Centennial</t>
+          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>coasl</t>
+          <t>coavr</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1677,23 +1677,23 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>All-States Cremation - Centennial</t>
+          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>coasl</t>
+          <t>coavr</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1702,18 +1702,18 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>All-States Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>coasc</t>
+          <t>coavr</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1727,18 +1727,18 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>All-States Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>coasc</t>
+          <t>coavr</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1758,12 +1758,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>All-States Cremation - Colorado Springs</t>
+          <t>All Veterans Funeral &amp; Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>coasc</t>
+          <t>coavr</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1777,18 +1777,18 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>All-States Cremation - Westminster</t>
+          <t>All-States Cremation - Centennial</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>coasw</t>
+          <t>coasl</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1808,12 +1808,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>All-States Cremation - Westminster</t>
+          <t>All-States Cremation - Centennial</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>coasw</t>
+          <t>coasl</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1833,12 +1833,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>All-States Cremation - Westminster</t>
+          <t>All-States Cremation - Centennial</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>coasw</t>
+          <t>coasl</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1858,12 +1858,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>All-States Cremation - Wheat Ridge</t>
+          <t>All-States Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>coasr</t>
+          <t>coasc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1877,18 +1877,18 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>All-States Cremation - Wheat Ridge</t>
+          <t>All-States Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>coasr</t>
+          <t>coasc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1908,12 +1908,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>All-States Cremation - Wheat Ridge</t>
+          <t>All-States Cremation - Colorado Springs</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>coasr</t>
+          <t>coasc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1927,23 +1927,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alpha Cremation Services</t>
+          <t>All-States Cremation - Westminster</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ormac</t>
+          <t>coasw</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1952,43 +1952,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alpha Cremation Services</t>
+          <t>All-States Cremation - Westminster</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ormac</t>
+          <t>coasw</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alpha Cremation Services</t>
+          <t>All-States Cremation - Westminster</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ormac</t>
+          <t>coasw</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alpha Cremation Services</t>
+          <t>All-States Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ormac</t>
+          <t>coasr</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2023,22 +2023,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alpha Cremation Services</t>
+          <t>All-States Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ormac</t>
+          <t>coasr</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2048,47 +2048,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Amador Hills Cremation &amp; Funeral Service</t>
+          <t>All-States Cremation - Wheat Ridge</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>cadll</t>
+          <t>coasr</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Amador Hills Cremation &amp; Funeral Service</t>
+          <t>Alpha Cremation Services</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>cadll</t>
+          <t>ormac</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2098,22 +2098,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Amador Hills Cremation &amp; Funeral Service</t>
+          <t>Alpha Cremation Services</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>cadll</t>
+          <t>ormac</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2133,12 +2133,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Amador Hills Cremation &amp; Funeral Service</t>
+          <t>Alpha Cremation Services</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>cadll</t>
+          <t>ormac</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2152,18 +2152,18 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Amador Hills Cremation &amp; Funeral Service</t>
+          <t>Alpha Cremation Services</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>cadll</t>
+          <t>ormac</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2177,18 +2177,18 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Amador Hills Cremation &amp; Funeral Service</t>
+          <t>Alpha Cremation Services</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>cadll</t>
+          <t>ormac</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2208,12 +2208,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Arvada</t>
+          <t>Amador Hills Cremation &amp; Funeral Service</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>coama</t>
+          <t>cadll</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2233,12 +2233,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Arvada</t>
+          <t>Amador Hills Cremation &amp; Funeral Service</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>coama</t>
+          <t>cadll</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2258,12 +2258,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Arvada</t>
+          <t>Amador Hills Cremation &amp; Funeral Service</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>coama</t>
+          <t>cadll</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Arvada</t>
+          <t>Amador Hills Cremation &amp; Funeral Service</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>coama</t>
+          <t>cadll</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2302,18 +2302,18 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Arvada</t>
+          <t>Amador Hills Cremation &amp; Funeral Service</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>coama</t>
+          <t>cadll</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2333,12 +2333,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Arvada</t>
+          <t>Amador Hills Cremation &amp; Funeral Service</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>coama</t>
+          <t>cadll</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2352,18 +2352,18 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Lakewood</t>
+          <t>Anderson McQueen Funeral Homes</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>coaml</t>
+          <t>flams</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2383,12 +2383,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Lakewood</t>
+          <t>Anderson McQueen Funeral Homes</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>coaml</t>
+          <t>flams</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2408,12 +2408,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Lakewood</t>
+          <t>Anderson McQueen Funeral Homes</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>coaml</t>
+          <t>flams</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2433,12 +2433,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Lakewood</t>
+          <t>Anderson McQueen Funeral Homes</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>coaml</t>
+          <t>flams</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2452,18 +2452,18 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Lakewood</t>
+          <t>Anderson McQueen Funeral Homes</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>coaml</t>
+          <t>flams</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2483,12 +2483,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Aspen Mortuaries - Lakewood</t>
+          <t>Anderson McQueen Funeral Homes</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>coaml</t>
+          <t>flams</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2502,18 +2502,18 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Blue Oaks Cremation &amp; Burial Services</t>
+          <t>Anderson McQueen Funeral Homes - Tyrone Family Tribute Center</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>cablo</t>
+          <t>flamt</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2533,12 +2533,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Blue Oaks Cremation &amp; Burial Services</t>
+          <t>Anderson McQueen Funeral Homes - Tyrone Family Tribute Center</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>cablo</t>
+          <t>flamt</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2558,12 +2558,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Blue Oaks Cremation &amp; Burial Services</t>
+          <t>Anderson McQueen Funeral Homes - Tyrone Family Tribute Center</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>cablo</t>
+          <t>flamt</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2583,12 +2583,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Blue Oaks Cremation &amp; Burial Services</t>
+          <t>Anderson McQueen Funeral Homes - Tyrone Family Tribute Center</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>cablo</t>
+          <t>flamt</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2608,12 +2608,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Blue Oaks Cremation &amp; Burial Services</t>
+          <t>Anderson McQueen Funeral Homes - Tyrone Family Tribute Center</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>cablo</t>
+          <t>flamt</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2633,12 +2633,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Blue Oaks Cremation &amp; Burial Services</t>
+          <t>Anderson McQueen Funeral Homes - Tyrone Family Tribute Center</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>cablo</t>
+          <t>flamt</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2658,12 +2658,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Brusie Funeral Home</t>
+          <t>Aspen Mortuaries - Arvada</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>cabru</t>
+          <t>coama</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2683,12 +2683,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Brusie Funeral Home</t>
+          <t>Aspen Mortuaries - Arvada</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>cabru</t>
+          <t>coama</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2708,12 +2708,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Brusie Funeral Home</t>
+          <t>Aspen Mortuaries - Arvada</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>cabru</t>
+          <t>coama</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Brusie Funeral Home</t>
+          <t>Aspen Mortuaries - Arvada</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>cabru</t>
+          <t>coama</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2752,18 +2752,18 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Brusie Funeral Home</t>
+          <t>Aspen Mortuaries - Arvada</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>cabru</t>
+          <t>coama</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2783,12 +2783,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Brusie Funeral Home</t>
+          <t>Aspen Mortuaries - Arvada</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>cabru</t>
+          <t>coama</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2802,18 +2802,18 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Canby Funeral Chapel</t>
+          <t>Aspen Mortuaries - Lakewood</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>orccf</t>
+          <t>coaml</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2833,12 +2833,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Canby Funeral Chapel</t>
+          <t>Aspen Mortuaries - Lakewood</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>orccf</t>
+          <t>coaml</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2858,12 +2858,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Canby Funeral Chapel</t>
+          <t>Aspen Mortuaries - Lakewood</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>orccf</t>
+          <t>coaml</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2883,12 +2883,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Canby Funeral Chapel</t>
+          <t>Aspen Mortuaries - Lakewood</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>orccf</t>
+          <t>coaml</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2902,18 +2902,18 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Canby Funeral Chapel</t>
+          <t>Aspen Mortuaries - Lakewood</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>orccf</t>
+          <t>coaml</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2933,12 +2933,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Canby Funeral Chapel</t>
+          <t>Aspen Mortuaries - Lakewood</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>orccf</t>
+          <t>coaml</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2952,18 +2952,18 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Portland</t>
+          <t>Atkins-Northland Funeral Home</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>orcmp</t>
+          <t>mnanf</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2977,18 +2977,18 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Portland</t>
+          <t>Atkins-Northland Funeral Home</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>orcmp</t>
+          <t>mnanf</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2998,47 +2998,47 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Portland</t>
+          <t>Atkins-Northland Funeral Home</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>orcmp</t>
+          <t>mnanf</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Portland</t>
+          <t>Atkins-Northland Funeral Home</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>orcmp</t>
+          <t>mnanf</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3048,22 +3048,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Portland</t>
+          <t>Atkins-Northland Funeral Home</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>orcmp</t>
+          <t>mnanf</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3073,47 +3073,47 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Salem</t>
+          <t>Atkins-Northland Funeral Home</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>orcms</t>
+          <t>mnanf</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Salem</t>
+          <t>Blue Oaks Cremation &amp; Burial Services</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>orcms</t>
+          <t>cablo</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3123,72 +3123,72 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Salem</t>
+          <t>Blue Oaks Cremation &amp; Burial Services</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>orcms</t>
+          <t>cablo</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Salem</t>
+          <t>Blue Oaks Cremation &amp; Burial Services</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>orcms</t>
+          <t>cablo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Salem</t>
+          <t>Blue Oaks Cremation &amp; Burial Services</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>orcms</t>
+          <t>cablo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3198,52 +3198,52 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Tualatin</t>
+          <t>Blue Oaks Cremation &amp; Burial Services</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>orcmt</t>
+          <t>cablo</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Tualatin</t>
+          <t>Blue Oaks Cremation &amp; Burial Services</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>orcmt</t>
+          <t>cablo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3252,23 +3252,23 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Tualatin</t>
+          <t>Brusie Funeral Home</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>orcmt</t>
+          <t>cabru</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3283,17 +3283,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Tualatin</t>
+          <t>Brusie Funeral Home</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>orcmt</t>
+          <t>cabru</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3302,23 +3302,23 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Crown Cremation Services - Tualatin</t>
+          <t>Brusie Funeral Home</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>orcmt</t>
+          <t>cabru</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3327,23 +3327,23 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Daneri Mortuary</t>
+          <t>Brusie Funeral Home</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>cadan</t>
+          <t>cabru</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3352,23 +3352,23 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Daneri Mortuary</t>
+          <t>Brusie Funeral Home</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>cadan</t>
+          <t>cabru</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3383,17 +3383,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Daneri Mortuary</t>
+          <t>Brusie Funeral Home</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>cadan</t>
+          <t>cabru</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3402,23 +3402,23 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Daneri Mortuary</t>
+          <t>Canby Funeral Chapel</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>cadan</t>
+          <t>orccf</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3427,23 +3427,23 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Daneri Mortuary</t>
+          <t>Canby Funeral Chapel</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>cadan</t>
+          <t>orccf</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3458,17 +3458,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Daneri Mortuary</t>
+          <t>Canby Funeral Chapel</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>cadan</t>
+          <t>orccf</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3477,23 +3477,23 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
+          <t>Canby Funeral Chapel</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>caaed</t>
+          <t>orccf</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3502,23 +3502,23 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
+          <t>Canby Funeral Chapel</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>caaed</t>
+          <t>orccf</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3533,17 +3533,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
+          <t>Canby Funeral Chapel</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>caaed</t>
+          <t>orccf</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3552,23 +3552,23 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
+          <t>Crown Cremation Services - Portland</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>caaed</t>
+          <t>orcmp</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3577,43 +3577,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
+          <t>Crown Cremation Services - Portland</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>caaed</t>
+          <t>orcmp</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
+          <t>Crown Cremation Services - Portland</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>caaed</t>
+          <t>orcmp</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3623,72 +3623,72 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Lane Memorial Funeral Home</t>
+          <t>Crown Cremation Services - Portland</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ormlm</t>
+          <t>orcmp</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Lane Memorial Funeral Home</t>
+          <t>Crown Cremation Services - Portland</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ormlm</t>
+          <t>orcmp</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Lane Memorial Funeral Home</t>
+          <t>Crown Cremation Services - Salem</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ormlm</t>
+          <t>orcms</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -3708,37 +3708,37 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Lane Memorial Funeral Home</t>
+          <t>Crown Cremation Services - Salem</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ormlm</t>
+          <t>orcms</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cremation</t>
+          <t>Burial</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Lane Memorial Funeral Home</t>
+          <t>Crown Cremation Services - Salem</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ormlm</t>
+          <t>orcms</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3748,22 +3748,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Lane Memorial Funeral Home</t>
+          <t>Crown Cremation Services - Salem</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ormlm</t>
+          <t>orcms</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3773,47 +3773,47 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>No Facilities</t>
+          <t>Facilities</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Molalla Funeral Chapel</t>
+          <t>Crown Cremation Services - Salem</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>orcmf</t>
+          <t>orcms</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Burial</t>
+          <t>Cremation</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>No Facilities</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Molalla Funeral Chapel</t>
+          <t>Crown Cremation Services - Tualatin</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>orcmf</t>
+          <t>orcmt</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Facilities</t>
+          <t>All</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Molalla Funeral Chapel</t>
+          <t>Crown Cremation Services - Tualatin</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>orcmf</t>
+          <t>orcmt</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3858,12 +3858,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Molalla Funeral Chapel</t>
+          <t>Crown Cremation Services - Tualatin</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>orcmf</t>
+          <t>orcmt</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3877,18 +3877,18 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Molalla Funeral Chapel</t>
+          <t>Crown Cremation Services - Tualatin</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>orcmf</t>
+          <t>orcmt</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3902,18 +3902,18 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Molalla Funeral Chapel</t>
+          <t>Crown Cremation Services - Tualatin</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>orcmf</t>
+          <t>orcmt</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3933,12 +3933,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Murphy-Musgrove Funeral Home</t>
+          <t>Daneri Mortuary</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ormmm</t>
+          <t>cadan</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3958,12 +3958,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Murphy-Musgrove Funeral Home</t>
+          <t>Daneri Mortuary</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ormmm</t>
+          <t>cadan</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3983,12 +3983,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Murphy-Musgrove Funeral Home</t>
+          <t>Daneri Mortuary</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ormmm</t>
+          <t>cadan</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4008,12 +4008,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Murphy-Musgrove Funeral Home</t>
+          <t>Daneri Mortuary</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ormmm</t>
+          <t>cadan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4033,12 +4033,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Murphy-Musgrove Funeral Home</t>
+          <t>Daneri Mortuary</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ormmm</t>
+          <t>cadan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4058,12 +4058,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Murphy-Musgrove Funeral Home</t>
+          <t>Daneri Mortuary</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ormmm</t>
+          <t>cadan</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4083,12 +4083,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Musgrove Family Mortuary</t>
+          <t>E James Reese Funeral Home</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ormwl</t>
+          <t>flamr</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4108,12 +4108,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Musgrove Family Mortuary</t>
+          <t>E James Reese Funeral Home</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ormwl</t>
+          <t>flamr</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4133,12 +4133,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Musgrove Family Mortuary</t>
+          <t>E James Reese Funeral Home</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ormwl</t>
+          <t>flamr</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4158,12 +4158,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Musgrove Family Mortuary</t>
+          <t>E James Reese Funeral Home</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ormwl</t>
+          <t>flamr</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4183,12 +4183,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Musgrove Family Mortuary</t>
+          <t>E James Reese Funeral Home</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ormwl</t>
+          <t>flamr</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4208,12 +4208,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Musgrove Family Mortuary</t>
+          <t>E James Reese Funeral Home</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ormwl</t>
+          <t>flamr</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4233,12 +4233,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ponderosa Valley Funeral Services</t>
+          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>copvp</t>
+          <t>caaed</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4258,12 +4258,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Ponderosa Valley Funeral Services</t>
+          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>copvp</t>
+          <t>caaed</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4283,12 +4283,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ponderosa Valley Funeral Services</t>
+          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>copvp</t>
+          <t>caaed</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4308,12 +4308,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ponderosa Valley Funeral Services</t>
+          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>copvp</t>
+          <t>caaed</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4333,12 +4333,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ponderosa Valley Funeral Services</t>
+          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>copvp</t>
+          <t>caaed</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4358,12 +4358,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ponderosa Valley Funeral Services</t>
+          <t>El Dorado Funeral &amp; Cremation Services - Placerville</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>copvp</t>
+          <t>caaed</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4383,12 +4383,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Aurora</t>
+          <t>Falconer Funeral Home</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>coroa</t>
+          <t>azflc</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4408,12 +4408,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Aurora</t>
+          <t>Falconer Funeral Home</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>coroa</t>
+          <t>azflc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4433,12 +4433,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Aurora</t>
+          <t>Falconer Funeral Home</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>coroa</t>
+          <t>azflc</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4458,12 +4458,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Aurora</t>
+          <t>Falconer Funeral Home</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>coroa</t>
+          <t>azflc</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4477,18 +4477,18 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Aurora</t>
+          <t>Falconer Funeral Home</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>coroa</t>
+          <t>azflc</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4508,12 +4508,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Aurora</t>
+          <t>Falconer Funeral Home</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>coroa</t>
+          <t>azflc</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4527,18 +4527,18 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Commerce City</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>coamc</t>
+          <t>flalg</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4558,12 +4558,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Commerce City</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>coamc</t>
+          <t>flalg</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4583,12 +4583,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Commerce City</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>coamc</t>
+          <t>flalg</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4608,12 +4608,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Commerce City</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>coamc</t>
+          <t>flalg</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4627,18 +4627,18 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Commerce City</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>coamc</t>
+          <t>flalg</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4658,12 +4658,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Commerce City</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>coamc</t>
+          <t>flalg</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4677,18 +4677,18 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Denver</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>corod</t>
+          <t>fllfm</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4708,12 +4708,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Denver</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>corod</t>
+          <t>fllfm</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4733,12 +4733,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Denver</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>corod</t>
+          <t>fllfm</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -4758,12 +4758,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Denver</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>corod</t>
+          <t>fllfm</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -4777,18 +4777,18 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Denver</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>corod</t>
+          <t>fllfm</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -4808,12 +4808,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Denver</t>
+          <t>Florida Mortuary Funeral &amp; Cremation Services</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>corod</t>
+          <t>fllfm</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -4827,18 +4827,18 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Lakewood</t>
+          <t>Lane Memorial Funeral Home</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>corol</t>
+          <t>ormlm</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4858,12 +4858,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Lakewood</t>
+          <t>Lane Memorial Funeral Home</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>corol</t>
+          <t>ormlm</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4883,12 +4883,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Lakewood</t>
+          <t>Lane Memorial Funeral Home</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>corol</t>
+          <t>ormlm</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4908,12 +4908,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Lakewood</t>
+          <t>Lane Memorial Funeral Home</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>corol</t>
+          <t>ormlm</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4927,18 +4927,18 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Lakewood</t>
+          <t>Lane Memorial Funeral Home</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>corol</t>
+          <t>ormlm</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4958,12 +4958,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Romero Funeral Home and Cremations - Lakewood</t>
+          <t>Lane Memorial Funeral Home</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>corol</t>
+          <t>ormlm</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -4977,18 +4977,18 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Springfield Memorial Funeral Home</t>
+          <t>Legacy Funeral Home – Chandler</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ormsm</t>
+          <t>azlgc</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5008,12 +5008,12 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Springfield Memorial Funeral Home</t>
+          <t>Legacy Funeral Home – Chandler</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ormsm</t>
+          <t>azlgc</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5033,12 +5033,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Springfield Memorial Funeral Home</t>
+          <t>Legacy Funeral Home – Chandler</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ormsm</t>
+          <t>azlgc</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5058,12 +5058,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Springfield Memorial Funeral Home</t>
+          <t>Legacy Funeral Home – Chandler</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>ormsm</t>
+          <t>azlgc</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5077,18 +5077,18 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Springfield Memorial Funeral Home</t>
+          <t>Legacy Funeral Home – Chandler</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ormsm</t>
+          <t>azlgc</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5102,18 +5102,18 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Springfield Memorial Funeral Home</t>
+          <t>Legacy Funeral Home – Chandler</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ormsm</t>
+          <t>azlgc</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5133,12 +5133,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>The Omega Society</t>
+          <t>Legacy Funeral Home – Rose Chapel</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>caoms</t>
+          <t>azlgm</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5158,12 +5158,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>The Omega Society</t>
+          <t>Legacy Funeral Home – Rose Chapel</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>caoms</t>
+          <t>azlgm</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5183,12 +5183,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>The Omega Society</t>
+          <t>Legacy Funeral Home – Rose Chapel</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>caoms</t>
+          <t>azlgm</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5208,12 +5208,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>The Omega Society</t>
+          <t>Legacy Funeral Home – Rose Chapel</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>caoms</t>
+          <t>azlgm</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5227,18 +5227,18 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>The Omega Society</t>
+          <t>Legacy Funeral Home – Rose Chapel</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>caoms</t>
+          <t>azlgm</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5252,18 +5252,18 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>The Omega Society</t>
+          <t>Legacy Funeral Home – Rose Chapel</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>caoms</t>
+          <t>azlgm</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5283,12 +5283,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - North</t>
+          <t>Loyless Funeral Homes - Arrangement Center</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>cotsn</t>
+          <t>fllta</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5302,18 +5302,18 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - North</t>
+          <t>Loyless Funeral Homes - Arrangement Center</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>cotsn</t>
+          <t>fllta</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5327,18 +5327,18 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - North</t>
+          <t>Loyless Funeral Homes - Arrangement Center</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>cotsn</t>
+          <t>fllta</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5358,12 +5358,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - North</t>
+          <t>Loyless Funeral Homes - Arrangement Center</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>cotsn</t>
+          <t>fllta</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5383,12 +5383,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - North</t>
+          <t>Loyless Funeral Homes - Arrangement Center</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>cotsn</t>
+          <t>fllta</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5408,12 +5408,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - North</t>
+          <t>Loyless Funeral Homes - Arrangement Center</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>cotsn</t>
+          <t>fllta</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5433,12 +5433,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - Platte</t>
+          <t>Loyless Funeral Homes - Land O' Lakes</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>cotsf</t>
+          <t>fllll</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5452,18 +5452,18 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - Platte</t>
+          <t>Loyless Funeral Homes - Land O' Lakes</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>cotsf</t>
+          <t>fllll</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5477,18 +5477,18 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - Platte</t>
+          <t>Loyless Funeral Homes - Land O' Lakes</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>cotsf</t>
+          <t>fllll</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5508,12 +5508,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - Platte</t>
+          <t>Loyless Funeral Homes - Land O' Lakes</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>cotsf</t>
+          <t>fllll</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5533,12 +5533,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - Platte</t>
+          <t>Loyless Funeral Homes - Land O' Lakes</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>cotsf</t>
+          <t>fllll</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5558,12 +5558,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>The Springs Funeral Services - Platte</t>
+          <t>Loyless Funeral Homes - Land O' Lakes</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>cotsf</t>
+          <t>fllll</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5583,12 +5583,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ullrey Memorial Chapel</t>
+          <t>Meldrum Mortuary &amp; Crematory</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>caulm</t>
+          <t>azmld</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5608,12 +5608,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ullrey Memorial Chapel</t>
+          <t>Meldrum Mortuary &amp; Crematory</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>caulm</t>
+          <t>azmld</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5633,12 +5633,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Ullrey Memorial Chapel</t>
+          <t>Meldrum Mortuary &amp; Crematory</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>caulm</t>
+          <t>azmld</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5658,12 +5658,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ullrey Memorial Chapel</t>
+          <t>Meldrum Mortuary &amp; Crematory</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>caulm</t>
+          <t>azmld</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5683,12 +5683,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Ullrey Memorial Chapel</t>
+          <t>Meldrum Mortuary &amp; Crematory</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>caulm</t>
+          <t>azmld</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5708,12 +5708,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Ullrey Memorial Chapel</t>
+          <t>Meldrum Mortuary &amp; Crematory</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>caulm</t>
+          <t>azmld</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5731,11 +5731,3261 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
-      <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Molalla Funeral Chapel</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>orcmf</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Molalla Funeral Chapel</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>orcmf</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Molalla Funeral Chapel</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>orcmf</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Molalla Funeral Chapel</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>orcmf</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Molalla Funeral Chapel</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>orcmf</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Molalla Funeral Chapel</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>orcmf</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Murphy-Musgrove Funeral Home</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ormmm</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Murphy-Musgrove Funeral Home</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ormmm</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Murphy-Musgrove Funeral Home</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ormmm</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Murphy-Musgrove Funeral Home</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ormmm</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Murphy-Musgrove Funeral Home</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ormmm</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Murphy-Musgrove Funeral Home</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ormmm</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Musgrove Family Mortuary</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ormwl</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Musgrove Family Mortuary</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ormwl</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Musgrove Family Mortuary</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ormwl</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Musgrove Family Mortuary</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ormwl</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Musgrove Family Mortuary</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ormwl</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Musgrove Family Mortuary</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ormwl</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Ponderosa Valley Funeral Services</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>copvp</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Ponderosa Valley Funeral Services</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>copvp</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Ponderosa Valley Funeral Services</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>copvp</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Ponderosa Valley Funeral Services</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>copvp</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Ponderosa Valley Funeral Services</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>copvp</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Ponderosa Valley Funeral Services</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>copvp</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Regency Mortuary</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>azrcy</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Regency Mortuary</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>azrcy</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Regency Mortuary</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>azrcy</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Regency Mortuary</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>azrcy</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Regency Mortuary</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>azrcy</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Regency Mortuary</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>azrcy</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Aurora</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>coroa</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Aurora</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>coroa</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Aurora</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>coroa</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Aurora</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>coroa</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Aurora</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>coroa</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Aurora</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>coroa</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Commerce City</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>coamc</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Commerce City</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>coamc</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Commerce City</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>coamc</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Commerce City</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>coamc</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Commerce City</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>coamc</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Commerce City</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>coamc</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Denver</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>corod</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Denver</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>corod</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Denver</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>corod</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Denver</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>corod</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Denver</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>corod</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Denver</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>corod</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Lakewood</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>corol</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Lakewood</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>corol</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Lakewood</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>corol</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Lakewood</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>corol</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Lakewood</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>corol</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Romero Funeral Home and Cremations - Lakewood</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>corol</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>azsfp</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>azsfp</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>azsfp</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>azsfp</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>azsfp</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>azsfp</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services - Ahwatukee</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>azsfa</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services - Ahwatukee</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>azsfa</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services - Ahwatukee</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>azsfa</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services - Ahwatukee</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>azsfa</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services - Ahwatukee</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>azsfa</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Samaritan Funeral &amp; Cremation Services - Ahwatukee</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>azsfa</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Sandberg Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>mnsan</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Sandberg Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>mnsan</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Sandberg Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>mnsan</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Sandberg Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>mnsan</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Sandberg Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>mnsan</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Sandberg Funeral &amp; Cremation Services</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>mnsan</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Spielman Mortuary</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>mnwsm</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Spielman Mortuary</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>mnwsm</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Spielman Mortuary</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>mnwsm</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Spielman Mortuary</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>mnwsm</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Spielman Mortuary</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>mnwsm</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Spielman Mortuary</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>mnwsm</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Springfield Memorial Funeral Home</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>ormsm</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Springfield Memorial Funeral Home</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ormsm</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Springfield Memorial Funeral Home</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>ormsm</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Springfield Memorial Funeral Home</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ormsm</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Springfield Memorial Funeral Home</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>ormsm</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Springfield Memorial Funeral Home</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>ormsm</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>The Omega Society</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>caoms</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>The Omega Society</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>caoms</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>The Omega Society</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>caoms</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>The Omega Society</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>caoms</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>The Omega Society</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>caoms</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>The Omega Society</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>caoms</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - North</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>cotsn</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - North</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>cotsn</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - North</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>cotsn</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - North</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>cotsn</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - North</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>cotsn</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - North</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>cotsn</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - North</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>cotsn</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - North</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>cotsn</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - Platte</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>cotsf</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - Platte</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>cotsf</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - Platte</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>cotsf</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - Platte</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>cotsf</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - Platte</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>cotsf</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>The Springs Funeral Services - Platte</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>cotsf</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Twin Cities Cremation</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>mnwtc</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Twin Cities Cremation</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>mnwtc</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Ullrey Memorial Chapel</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>caulm</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Ullrey Memorial Chapel</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>caulm</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Ullrey Memorial Chapel</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>caulm</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Ullrey Memorial Chapel</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>caulm</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Ullrey Memorial Chapel</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>caulm</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Ullrey Memorial Chapel</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>caulm</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - Grand Avenue</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>mnwga</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - Grand Avenue</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>mnwga</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - Grand Avenue</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>mnwga</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - Grand Avenue</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>mnwga</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - Grand Avenue</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>mnwga</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - Grand Avenue</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>mnwga</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - West-Heights</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>mnwwh</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - West-Heights</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>mnwwh</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - West-Heights</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>mnwwh</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - West-Heights</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>mnwwh</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - West-Heights</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>mnwwh</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Willwerscheid Funeral Home &amp; Cremation Service - West-Heights</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>mnwwh</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Wyman Cremation &amp; Burial Chapel</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>azwym</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Wyman Cremation &amp; Burial Chapel</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>azwym</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Wyman Cremation &amp; Burial Chapel</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>azwym</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Burial</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Wyman Cremation &amp; Burial Chapel</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>azwym</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Wyman Cremation &amp; Burial Chapel</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>azwym</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Facilities</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Wyman Cremation &amp; Burial Chapel</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>azwym</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Cremation</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>No Facilities</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr"/>
+      <c r="B343" t="inlineStr"/>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
